--- a/Final_Figures_and_Sheets_Superset/pc_summary_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Superset/pc_summary_statistics.xlsx
@@ -717,37 +717,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008717382153061114</v>
+        <v>1.998083089036456e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.998083089036456e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001547896233658058</v>
+        <v>2.825716203263684e-05</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004387668199625277</v>
+        <v>3.996166178072911e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4181980463339483</v>
+        <v>0.009585382739639638</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.418x</t>
+          <t>0.010x</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.007064553337856572</v>
+        <v>0.0001619243519226764</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.007x</t>
+          <t>0.000x</t>
         </is>
       </c>
     </row>
@@ -786,11 +786,11 @@
         <v>2.421027674426409e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.704861933219134e-05</v>
+        <v>0.0007438095578520053</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.000x</t>
+          <t>0.001x</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1024,37 +1024,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0001369204617329698</v>
+        <v>1.033065535198196e-07</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.033065535198196e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0004059976990106821</v>
+        <v>1.460975290697508e-07</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.001578391707320189</v>
+        <v>2.066131070396391e-07</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4001220473535384</v>
+        <v>0.000301892275093276</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.400x</t>
+          <t>0.000x</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.001935140970509227</v>
+        <v>1.460064782926225e-06</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.002x</t>
+          <t>0.000x</t>
         </is>
       </c>
     </row>
@@ -1093,11 +1093,11 @@
         <v>3.804200731235569e-08</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001545867295395122</v>
+        <v>0.2048861922615488</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.000x</t>
+          <t>0.205x</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1331,37 +1331,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002986583860895246</v>
+        <v>0.0006974888556878712</v>
       </c>
       <c r="F18" t="n">
-        <v>0.001203791263138444</v>
+        <v>0.0006974888556878712</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003485569988878292</v>
+        <v>0.0008776914585226337</v>
       </c>
       <c r="H18" t="n">
-        <v>8.38635049161365e-05</v>
+        <v>7.68672735770055e-05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.009676759149110353</v>
+        <v>0.001318110437798737</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5226493483639382</v>
+        <v>0.1220598894574824</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.523x</t>
+          <t>0.122x</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0.01945390371548543</v>
+        <v>0.00454327809737397</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.019x</t>
+          <t>0.005x</t>
         </is>
       </c>
     </row>
@@ -1400,11 +1400,11 @@
         <v>0.0001720323163889472</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03348690001099775</v>
+        <v>0.1433878610513803</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.033x</t>
+          <t>0.143x</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1638,37 +1638,37 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0006453408716290414</v>
+        <v>9.265695102986672e-05</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0001156231221074556</v>
+        <v>9.265695102986672e-05</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001441387489946252</v>
+        <v>2.232997599933299e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>4.527134128291297e-05</v>
+        <v>7.68672735770055e-05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00560472251134382</v>
+        <v>0.0001084466284827279</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4385578336534436</v>
+        <v>0.06296739212257713</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.439x</t>
+          <t>0.063x</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.007534546809865179</v>
+        <v>0.001081797489490513</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.008x</t>
+          <t>0.001x</t>
         </is>
       </c>
     </row>
@@ -1707,11 +1707,11 @@
         <v>0.0001720323163889472</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1805666077883538</v>
+        <v>1.257617596543562</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.181x</t>
+          <t>1.258x</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1945,37 +1945,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.004697381448048906</v>
+        <v>0.00180008939207676</v>
       </c>
       <c r="F30" t="n">
-        <v>0.001272563071040687</v>
+        <v>0.00180008939207676</v>
       </c>
       <c r="G30" t="n">
-        <v>0.006209460863732814</v>
+        <v>0.002495543482126223</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>3.547367311941806e-05</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01895001912533469</v>
+        <v>0.003564705111034102</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7214543597324931</v>
+        <v>0.2764694232701518</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.721x</t>
+          <t>0.276x</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.03043145204663082</v>
+        <v>0.01166167462031123</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.030x</t>
+          <t>0.012x</t>
         </is>
       </c>
     </row>
@@ -2014,11 +2014,11 @@
         <v>1.701669145658016e-05</v>
       </c>
       <c r="J31" t="n">
-        <v>0.002897051496927236</v>
+        <v>0.007559933420866474</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.003x</t>
+          <t>0.008x</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -2252,37 +2252,37 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0005005173497504655</v>
+        <v>0.0001649658930843719</v>
       </c>
       <c r="F36" t="n">
-        <v>0.000189839907483524</v>
+        <v>0.0001649658930843719</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0007779175941242673</v>
+        <v>0.0001831296536962378</v>
       </c>
       <c r="H36" t="n">
-        <v>3.563919320643563e-05</v>
+        <v>3.547367311941806e-05</v>
       </c>
       <c r="I36" t="n">
-        <v>0.002805858397822578</v>
+        <v>0.0002944581130493257</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5253641062142128</v>
+        <v>0.1731551544003592</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.525x</t>
+          <t>0.173x</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.005743478701873426</v>
+        <v>0.001892997503359248</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.006x</t>
+          <t>0.002x</t>
         </is>
       </c>
     </row>
@@ -2321,11 +2321,11 @@
         <v>1.701669145658016e-05</v>
       </c>
       <c r="J37" t="n">
-        <v>0.02805843402432324</v>
+        <v>0.08513113088667296</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.028x</t>
+          <t>0.085x</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -2559,37 +2559,37 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0007975681324907098</v>
+        <v>1.998083089036456e-05</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1.998083089036456e-05</v>
       </c>
       <c r="G42" t="n">
-        <v>0.001437604252366915</v>
+        <v>2.825716203263684e-05</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.004237778913302674</v>
+        <v>3.996166178072911e-05</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4199748893940973</v>
+        <v>0.01052129203931146</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.420x</t>
+          <t>0.011x</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0.00670378446670232</v>
+        <v>0.0001679445031690657</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.007x</t>
+          <t>0.000x</t>
         </is>
       </c>
     </row>
@@ -2628,11 +2628,11 @@
         <v>1.8798567824958e-08</v>
       </c>
       <c r="J43" t="n">
-        <v>1.531401311139329e-05</v>
+        <v>0.0006112843307273168</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.000x</t>
+          <t>0.001x</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -2864,37 +2864,37 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0001260382510290351</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0003953311323045136</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.001533789027633637</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0.400x</t>
+          <t>0.000x</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.001797051853381348</v>
+        <v>0</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0.002x</t>
+          <t>0.000x</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2932,10 @@
       <c r="I49" t="n">
         <v>3.361573602129544e-08</v>
       </c>
-      <c r="J49" t="n">
-        <v>0.0001391082794862425</v>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.000x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -3171,37 +3169,37 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.002000508003911323</v>
+        <v>0.000350849024089893</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0005698228764310819</v>
+        <v>0.000350849024089893</v>
       </c>
       <c r="G54" t="n">
-        <v>0.002591057975854067</v>
+        <v>0.0004959158500263177</v>
       </c>
       <c r="H54" t="n">
-        <v>4.048582995951417e-05</v>
+        <v>1.83563638392849e-07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.007119741100323625</v>
+        <v>0.0007015144845413931</v>
       </c>
       <c r="J54" t="n">
-        <v>0.4919758837180819</v>
+        <v>0.08628271336119231</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0.492x</t>
+          <t>0.086x</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.01400899486145927</v>
+        <v>0.002456897031160881</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>0.014x</t>
+          <t>0.002x</t>
         </is>
       </c>
     </row>
@@ -3240,11 +3238,11 @@
         <v>3.359567535096329e-05</v>
       </c>
       <c r="J55" t="n">
-        <v>0.008304308435942646</v>
+        <v>0.04735038250753441</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.008x</t>
+          <t>0.047x</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -3478,37 +3476,37 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0005102872732289484</v>
+        <v>1.730494933678769e-05</v>
       </c>
       <c r="F60" t="n">
-        <v>8.387879873745994e-06</v>
+        <v>1.730494933678769e-05</v>
       </c>
       <c r="G60" t="n">
-        <v>0.001407676038317402</v>
+        <v>2.421329586129073e-05</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1.83563638392849e-07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.005405462889561937</v>
+        <v>3.442633503518254e-05</v>
       </c>
       <c r="J60" t="n">
-        <v>0.4056438824396519</v>
+        <v>0.01375626476039226</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0.406x</t>
+          <t>0.014x</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.006135686412383997</v>
+        <v>0.0002080744476358583</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>0.006x</t>
+          <t>0.000x</t>
         </is>
       </c>
     </row>
@@ -3547,11 +3545,11 @@
         <v>3.359567535096329e-05</v>
       </c>
       <c r="J61" t="n">
-        <v>0.04438182774849875</v>
+        <v>1.308728585211931</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>0.044x</t>
+          <t>1.309x</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -3785,37 +3783,37 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0.004408986963751724</v>
+        <v>0.001603530515316153</v>
       </c>
       <c r="F66" t="n">
-        <v>0.001225648303444717</v>
+        <v>0.001603530515316153</v>
       </c>
       <c r="G66" t="n">
-        <v>0.006056380445464147</v>
+        <v>0.002267539903798991</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1.376727287946367e-07</v>
       </c>
       <c r="I66" t="n">
-        <v>0.01867642058736028</v>
+        <v>0.003206923357903511</v>
       </c>
       <c r="J66" t="n">
-        <v>0.6979370539268804</v>
+        <v>0.2538368502657768</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0.698x</t>
+          <t>0.254x</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0.02862691475798404</v>
+        <v>0.01041149174428964</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>0.029x</t>
+          <t>0.010x</t>
         </is>
       </c>
     </row>
@@ -3854,11 +3852,11 @@
         <v>9.542409372055383e-06</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0015704349679927</v>
+        <v>0.004317989109134306</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.002x</t>
+          <t>0.004x</t>
         </is>
       </c>
       <c r="L67" t="n">
@@ -4092,37 +4090,37 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0003699147188897518</v>
+        <v>0.0001256597613290366</v>
       </c>
       <c r="F72" t="n">
-        <v>2.536018905463165e-05</v>
+        <v>0.0001256597613290366</v>
       </c>
       <c r="G72" t="n">
-        <v>0.000735882791309071</v>
+        <v>0.0001775150400758595</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1.376727287946367e-07</v>
       </c>
       <c r="I72" t="n">
-        <v>0.002446759812568519</v>
+        <v>0.0002511818499292787</v>
       </c>
       <c r="J72" t="n">
-        <v>0.4643016764621604</v>
+        <v>0.1577229422609035</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0.464x</t>
+          <t>0.158x</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.00426219814213952</v>
+        <v>0.001447865613149446</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0.004x</t>
+          <t>0.001x</t>
         </is>
       </c>
     </row>
@@ -4161,11 +4159,11 @@
         <v>9.542409372055383e-06</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01465119476949192</v>
+        <v>0.04312989724979892</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0.015x</t>
+          <t>0.043x</t>
         </is>
       </c>
       <c r="L73" t="n">

--- a/Final_Figures_and_Sheets_Superset/pc_summary_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Superset/pc_summary_statistics.xlsx
@@ -562,37 +562,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003863169574817671</v>
+        <v>0.004962322393111182</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002615933412604043</v>
+        <v>0.001856535586694317</v>
       </c>
       <c r="G3" t="n">
-        <v>0.004211922110339287</v>
+        <v>0.007347830830965029</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01888810884899542</v>
+        <v>0.03254132231404959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03130706791935315</v>
+        <v>0.04021458576697119</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.031x</t>
+          <t>0.040x</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.03130706791935315</v>
+        <v>0.04021458576697119</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.031x</t>
+          <t>0.040x</t>
         </is>
       </c>
     </row>
@@ -632,11 +632,11 @@
         <v>0.0005690102777481419</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04909701448755735</v>
+        <v>0.03822204152757561</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.049x</t>
+          <t>0.038x</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1176,37 +1176,37 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0270302583530731</v>
+        <v>0.02973927276910436</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01052521155325547</v>
+        <v>0.01002731165898068</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0371458953933673</v>
+        <v>0.04311019545593976</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1338353005019672</v>
+        <v>0.1730523627075351</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1760687353502791</v>
+        <v>0.1937146170894032</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.176x</t>
+          <t>0.194x</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.1760687353502791</v>
+        <v>0.1937146170894032</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.176x</t>
+          <t>0.194x</t>
         </is>
       </c>
     </row>
@@ -1246,11 +1246,11 @@
         <v>0.004412514966942579</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07273015474656162</v>
+        <v>0.06610500828725385</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.073x</t>
+          <t>0.066x</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1790,37 +1790,37 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01317731216760816</v>
+        <v>0.01799049604619476</v>
       </c>
       <c r="F27" t="n">
-        <v>0.007955062017014092</v>
+        <v>0.006699632021885506</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01448772915757205</v>
+        <v>0.04923130678847103</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.06744025735294118</v>
+        <v>0.3612068965517241</v>
       </c>
       <c r="J27" t="n">
-        <v>0.08536771981730652</v>
+        <v>0.1165493847539838</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.085x</t>
+          <t>0.117x</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0.08536771981730652</v>
+        <v>0.1165493847539838</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.085x</t>
+          <t>0.117x</t>
         </is>
       </c>
     </row>
@@ -1860,11 +1860,11 @@
         <v>0.01895001912533469</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5292522714994019</v>
+        <v>0.3876559256095915</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.529x</t>
+          <t>0.388x</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -2404,37 +2404,37 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E39" t="n">
-        <v>0.002763445052922336</v>
+        <v>0.002964521997024178</v>
       </c>
       <c r="F39" t="n">
-        <v>0.00163769211388259</v>
+        <v>0.0006031249374148842</v>
       </c>
       <c r="G39" t="n">
-        <v>0.003782499575365437</v>
+        <v>0.005008898523871809</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.01678200113662956</v>
+        <v>0.02492163009404389</v>
       </c>
       <c r="J39" t="n">
-        <v>0.02322753287861826</v>
+        <v>0.02491764114594876</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.023x</t>
+          <t>0.025x</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.02322753287861826</v>
+        <v>0.02491764114594876</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.023x</t>
+          <t>0.025x</t>
         </is>
       </c>
     </row>
@@ -2474,11 +2474,11 @@
         <v>0.0005690102777481419</v>
       </c>
       <c r="J40" t="n">
-        <v>0.06863537683954972</v>
+        <v>0.06397999163882306</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.069x</t>
+          <t>0.064x</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -3014,16 +3014,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0183403715996476</v>
+        <v>0.01685383548180843</v>
       </c>
       <c r="F51" t="n">
-        <v>0.006817281014665081</v>
+        <v>0.005390588934741554</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02816296895494138</v>
+        <v>0.02684572963874532</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -3032,19 +3032,19 @@
         <v>0.1298374481398354</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1284324636514205</v>
+        <v>0.118022669341442</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.128x</t>
+          <t>0.118x</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.1284324636514205</v>
+        <v>0.118022669341442</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.128x</t>
+          <t>0.118x</t>
         </is>
       </c>
     </row>
@@ -3084,11 +3084,11 @@
         <v>0.001994898224790463</v>
       </c>
       <c r="J52" t="n">
-        <v>0.05545135349828925</v>
+        <v>0.06034225443577896</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.055x</t>
+          <t>0.060x</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -3628,37 +3628,37 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E63" t="n">
-        <v>0.01289240147639008</v>
+        <v>0.01782030571915158</v>
       </c>
       <c r="F63" t="n">
-        <v>0.007955062017014092</v>
+        <v>0.006677088898509607</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01446740325575995</v>
+        <v>0.04924877471640624</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0.06744025735294118</v>
+        <v>0.3612068965517241</v>
       </c>
       <c r="J63" t="n">
-        <v>0.08370849837493627</v>
+        <v>0.1157046679832493</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0.084x</t>
+          <t>0.116x</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0.08370849837493627</v>
+        <v>0.1157046679832493</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>0.084x</t>
+          <t>0.116x</t>
         </is>
       </c>
     </row>
@@ -3698,11 +3698,11 @@
         <v>0.01867642058736028</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5304752443202754</v>
+        <v>0.3837812847235885</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0.530x</t>
+          <t>0.384x</t>
         </is>
       </c>
       <c r="L64" t="n">

--- a/Final_Figures_and_Sheets_Superset/pc_summary_statistics.xlsx
+++ b/Final_Figures_and_Sheets_Superset/pc_summary_statistics.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -557,8 +557,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -609,8 +608,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -661,8 +659,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -713,7 +710,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -764,37 +761,35 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1.486193299007775e-08</v>
+        <v>8.7710385535849e-10</v>
       </c>
       <c r="F7" t="n">
-        <v>1.949841837061067e-08</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.233823272510336e-08</v>
-      </c>
+        <v>8.7710385535849e-10</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>8.7710385535849e-10</v>
       </c>
       <c r="I7" t="n">
-        <v>2.421027674426409e-08</v>
+        <v>8.7710385535849e-10</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007438095578520053</v>
+        <v>4.389726634348622e-05</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.001x</t>
+          <t>0.000x</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.204408806090784e-07</v>
+        <v>7.108036403846121e-09</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -815,7 +810,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -864,8 +859,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -916,8 +910,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -968,8 +961,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1020,7 +1012,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1071,37 +1063,35 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>2.116608638633973e-08</v>
+        <v>1.245975102399426e-09</v>
       </c>
       <c r="F13" t="n">
-        <v>2.421027674426409e-08</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.858594409225677e-08</v>
-      </c>
+        <v>1.245975102399426e-09</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1.245975102399426e-09</v>
       </c>
       <c r="I13" t="n">
-        <v>3.804200731235569e-08</v>
+        <v>1.245975102399426e-09</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2048861922615488</v>
+        <v>0.01206094928101907</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.205x</t>
+          <t>0.012x</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.99147113828939e-07</v>
+        <v>1.760976729387531e-08</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1122,7 +1112,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1171,8 +1161,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1223,8 +1212,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1275,8 +1263,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1327,7 +1314,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1378,41 +1365,39 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0001000114351242587</v>
+        <v>6.609534173726737e-05</v>
       </c>
       <c r="F19" t="n">
         <v>6.609534173726737e-05</v>
       </c>
-      <c r="G19" t="n">
-        <v>6.240706525699538e-05</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>6.190664724656162e-05</v>
+        <v>6.609534173726737e-05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0001720323163889472</v>
+        <v>6.609534173726737e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1433878610513803</v>
+        <v>0.0947618606351544</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.143x</t>
+          <t>0.095x</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.0006514509285440382</v>
+        <v>0.0004305294858901016</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.001x</t>
+          <t>0.000x</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1414,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1478,8 +1463,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1530,8 +1514,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1582,8 +1565,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1634,7 +1616,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1685,37 +1667,35 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0001165270120572355</v>
+        <v>8.978999592653821e-05</v>
       </c>
       <c r="F25" t="n">
         <v>8.978999592653821e-05</v>
       </c>
-      <c r="G25" t="n">
-        <v>4.807973193844635e-05</v>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>8.775872385622115e-05</v>
+        <v>8.978999592653821e-05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0001720323163889472</v>
+        <v>8.978999592653821e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>1.257617596543562</v>
+        <v>0.9690583915026042</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.258x</t>
+          <t>0.969x</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0.001360487558679918</v>
+        <v>0.001048324935097232</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1736,7 +1716,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1785,8 +1765,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1837,8 +1816,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1889,8 +1867,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1941,7 +1918,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1992,37 +1969,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1.360855595570831e-05</v>
+        <v>1.066659492406927e-05</v>
       </c>
       <c r="F31" t="n">
-        <v>1.314238148647551e-05</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3.200612514796985e-06</v>
-      </c>
+        <v>1.066659492406927e-05</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>1.066659492406927e-05</v>
       </c>
       <c r="I31" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>1.066659492406927e-05</v>
       </c>
       <c r="J31" t="n">
-        <v>0.007559933420866474</v>
+        <v>0.005925591790618373</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.008x</t>
+          <t>0.006x</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>8.816148370536123e-05</v>
+        <v>6.910232339497886e-05</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2043,7 +2018,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2092,8 +2067,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2144,8 +2118,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2196,8 +2169,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2248,7 +2220,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2299,37 +2271,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1.404373303600256e-05</v>
+        <v>1.044117906365516e-05</v>
       </c>
       <c r="F37" t="n">
-        <v>1.467332858777236e-05</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3.332661657967069e-06</v>
-      </c>
+        <v>1.044117906365516e-05</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>1.044117906365516e-05</v>
       </c>
       <c r="I37" t="n">
-        <v>1.701669145658016e-05</v>
+        <v>1.044117906365516e-05</v>
       </c>
       <c r="J37" t="n">
-        <v>0.08513113088667296</v>
+        <v>0.06329295631015686</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.085x</t>
+          <t>0.063x</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.0001611530182266213</v>
+        <v>0.0001198134082753529</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2350,7 +2320,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2399,8 +2369,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2451,8 +2420,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2503,8 +2471,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2555,7 +2522,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2606,37 +2573,35 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1.22139688381922e-08</v>
+        <v>1.349390546705369e-10</v>
       </c>
       <c r="F43" t="n">
-        <v>1.770839963494805e-08</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1.047493852268498e-08</v>
-      </c>
+        <v>1.349390546705369e-10</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>1.349390546705369e-10</v>
       </c>
       <c r="I43" t="n">
-        <v>1.8798567824958e-08</v>
+        <v>1.349390546705369e-10</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0006112843307273168</v>
+        <v>6.753425591305573e-06</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.001x</t>
+          <t>0.000x</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.02661843219034e-07</v>
+        <v>1.134200705621068e-09</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2657,7 +2622,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2706,8 +2671,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2758,8 +2722,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2810,8 +2773,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2860,7 +2822,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2911,26 +2873,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1.75329642501042e-08</v>
+        <v>1.845889040591741e-10</v>
       </c>
       <c r="F49" t="n">
-        <v>1.8798567824958e-08</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1.675146900125734e-08</v>
-      </c>
+        <v>1.845889040591741e-10</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>1.845889040591741e-10</v>
       </c>
       <c r="I49" t="n">
-        <v>3.361573602129544e-08</v>
+        <v>1.845889040591741e-10</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
@@ -2939,7 +2899,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.499847914714426e-07</v>
+        <v>2.631866353625887e-09</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -2960,7 +2920,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -3009,8 +2969,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -3061,8 +3020,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -3113,8 +3071,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -3165,7 +3122,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -3216,37 +3173,35 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>1.661283549305159e-05</v>
+        <v>7.793067754860183e-07</v>
       </c>
       <c r="F55" t="n">
-        <v>1.546352435270545e-05</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1.643834537577872e-05</v>
-      </c>
+        <v>7.793067754860183e-07</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>7.793067754860183e-07</v>
       </c>
       <c r="I55" t="n">
-        <v>3.359567535096329e-05</v>
+        <v>7.793067754860183e-07</v>
       </c>
       <c r="J55" t="n">
-        <v>0.04735038250753441</v>
+        <v>0.002221202631267254</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.047x</t>
+          <t>0.002x</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.0001163350142070934</v>
+        <v>5.457266150367252e-06</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -3267,7 +3222,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -3316,8 +3271,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -3368,8 +3322,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -3420,8 +3373,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3472,7 +3424,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -3523,37 +3475,35 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>2.26474818626983e-05</v>
+        <v>1.35988030037174e-05</v>
       </c>
       <c r="F61" t="n">
-        <v>2.074796723341422e-05</v>
-      </c>
-      <c r="G61" t="n">
-        <v>1.013285955632269e-05</v>
-      </c>
+        <v>1.35988030037174e-05</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>1.35988030037174e-05</v>
       </c>
       <c r="I61" t="n">
-        <v>3.359567535096329e-05</v>
+        <v>1.35988030037174e-05</v>
       </c>
       <c r="J61" t="n">
-        <v>1.308728585211931</v>
+        <v>0.7858331590031536</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1.309x</t>
+          <t>0.786x</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.0002723129774732308</v>
+        <v>0.0001635118004935228</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -3574,7 +3524,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -3623,8 +3573,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -3675,8 +3624,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3727,8 +3675,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3779,7 +3726,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3830,37 +3777,35 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>6.92402730129967e-06</v>
+        <v>4.191510650939885e-06</v>
       </c>
       <c r="F67" t="n">
-        <v>7.038161880903741e-06</v>
-      </c>
-      <c r="G67" t="n">
-        <v>2.677274604444773e-06</v>
-      </c>
+        <v>4.191510650939885e-06</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>4.191510650939885e-06</v>
       </c>
       <c r="I67" t="n">
-        <v>9.542409372055383e-06</v>
+        <v>4.191510650939885e-06</v>
       </c>
       <c r="J67" t="n">
-        <v>0.004317989109134306</v>
+        <v>0.002613926339975816</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.004x</t>
+          <t>0.003x</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.495670796168442e-05</v>
+        <v>2.721487250883945e-05</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -3881,7 +3826,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>L1: within sample</t>
+          <t>Single mouse</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3930,8 +3875,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>L2: within superset
-across mice</t>
+          <t>Same strain, same epitope</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3982,8 +3926,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>L3: within epitope
-across strain</t>
+          <t>Same epitope, different strain</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -4034,8 +3977,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>L4: within strain
-across epitope</t>
+          <t>Same strain, different epitope</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -4086,7 +4028,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>L5: all supersets</t>
+          <t>Cross-strain baseline</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -4137,37 +4079,35 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>L6: pre-immune</t>
+          <t>Pre-immune repertoires</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>5.419692594555606e-06</v>
+        <v>2.486827862711209e-06</v>
       </c>
       <c r="F73" t="n">
-        <v>4.229840548900228e-06</v>
-      </c>
-      <c r="G73" t="n">
-        <v>3.675203195289013e-06</v>
-      </c>
+        <v>2.486827862711209e-06</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>2.486827862711209e-06</v>
       </c>
       <c r="I73" t="n">
-        <v>9.542409372055383e-06</v>
+        <v>2.486827862711209e-06</v>
       </c>
       <c r="J73" t="n">
-        <v>0.04312989724979892</v>
+        <v>0.01979016859820001</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0.043x</t>
+          <t>0.020x</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>6.244629512665272e-05</v>
+        <v>2.865350459176377e-05</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
